--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3882,8 +3998,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3902,893 +4022,896 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥 타령 — 민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O3" s="15"/>
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="K4" s="16"/>
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="16"/>
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="16"/>
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="17"/>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="17"/>
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="17"/>
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="M5" s="17"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="17"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="15"/>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="15"/>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="16"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E7" s="16"/>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ﾉ</t>
-        </is>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="16"/>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="16"/>
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="16"/>
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="17"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="17"/>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="17"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="17"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="17"/>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="17"/>
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="15"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="15"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="15"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O9" s="15"/>
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="16"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="16"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="16"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="16"/>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="M10" s="16"/>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="16"/>
+      <c r="P10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="17"/>
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="17"/>
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="17"/>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="17"/>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="17"/>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="17"/>
+      <c r="P11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="15"/>
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="E13" s="16"/>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="16"/>
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="16"/>
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="16"/>
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="16"/>
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="17"/>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G14" s="17"/>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="17"/>
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M14" s="17"/>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="17"/>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="P6" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="I8" s="13"/>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4359,112 +4412,112 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">흥 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈에</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈깨</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나도</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">성화</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4472,82 +4525,82 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">으을</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이나</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나도</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로다</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4555,82 +4608,82 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">았다</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">서어</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈속</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가아</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4638,149 +4691,149 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꾸</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="24"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이오</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로다</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q6" s="11"/>
+      <c r="Q6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">살고</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">요오</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -4788,63 +4841,63 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">서어</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">써아</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="28"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="O8" s="27"/>
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">고오</t>
         </is>
@@ -4852,84 +4905,84 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깨라</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈에</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깨인</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이것</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="O9" s="22"/>
+      <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어허</t>
         </is>
@@ -4937,155 +4990,155 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">느은</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">주어</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈도</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">저것이</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">두우</t>
         </is>
       </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가아</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5093,77 +5146,77 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="30"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가는</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">련만</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">로다</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈이</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="Q12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어어</t>
         </is>
@@ -5171,73 +5224,73 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="31"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아안</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로다</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5245,65 +5298,65 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="32"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">새영</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아ㄴ</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -4389,28 +4389,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4523,11 +4523,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="25"/>
@@ -4606,17 +4606,17 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="24"/>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4781,13 +4781,13 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="26" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="25"/>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M7" s="25"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="27"/>
@@ -4888,7 +4888,7 @@
       <c r="M8" s="27"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O8" s="27"/>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5061,12 +5061,12 @@
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5296,11 +5296,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5333,13 +5333,13 @@
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="27"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -4465,7 +4465,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈에</t>
+          <t xml:space="preserve">꿈
+에</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -4476,7 +4477,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈깨</t>
+          <t xml:space="preserve">꿈
+깨</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -4487,7 +4489,8 @@
       </c>
       <c r="K3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">나도</t>
+          <t xml:space="preserve">나
+도</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
@@ -4498,7 +4501,8 @@
       </c>
       <c r="M3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="N3" s="21" t="inlineStr">
@@ -4509,7 +4513,8 @@
       </c>
       <c r="O3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">성화</t>
+          <t xml:space="preserve">성
+화</t>
         </is>
       </c>
       <c r="P3" s="23" t="inlineStr">
@@ -4532,7 +4537,8 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">으을</t>
+          <t xml:space="preserve">으
+을</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -4564,7 +4570,8 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이나</t>
+          <t xml:space="preserve">이
+나</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -4575,7 +4582,8 @@
       </c>
       <c r="K4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">나도</t>
+          <t xml:space="preserve">나
+도</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
@@ -4586,7 +4594,8 @@
       </c>
       <c r="M4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">로다</t>
+          <t xml:space="preserve">로
+다</t>
         </is>
       </c>
       <c r="N4" s="21" t="inlineStr">
@@ -4621,7 +4630,8 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">았다</t>
+          <t xml:space="preserve">았
+다</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -4632,7 +4642,8 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">서어</t>
+          <t xml:space="preserve">서
+어</t>
         </is>
       </c>
       <c r="H5" s="23" t="inlineStr">
@@ -4654,7 +4665,8 @@
       </c>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈속</t>
+          <t xml:space="preserve">꿈
+속</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -4665,7 +4677,8 @@
       </c>
       <c r="M5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -4675,7 +4688,8 @@
       </c>
       <c r="O5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">가아</t>
+          <t xml:space="preserve">가
+아</t>
         </is>
       </c>
       <c r="P5" s="21" t="inlineStr">
@@ -4715,7 +4729,8 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -4725,7 +4740,9 @@
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이오</t>
+          <t xml:space="preserve">꿈
+이
+오</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -4746,7 +4763,8 @@
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">로다</t>
+          <t xml:space="preserve">로
+다</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -4792,7 +4810,8 @@
       </c>
       <c r="G7" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">살고</t>
+          <t xml:space="preserve">살
+고</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -4809,7 +4828,8 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">요오</t>
+          <t xml:space="preserve">요
+오</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -4848,7 +4868,8 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">서어</t>
+          <t xml:space="preserve">서
+어</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -4858,7 +4879,8 @@
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">써아</t>
+          <t xml:space="preserve">써
+아</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -4899,7 +4921,8 @@
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">고오</t>
+          <t xml:space="preserve">고
+오</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4946,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨라</t>
+          <t xml:space="preserve">깨
+라</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -4934,7 +4958,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈에</t>
+          <t xml:space="preserve">꿈
+에</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -4945,7 +4970,8 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨인</t>
+          <t xml:space="preserve">깨
+인</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -4956,7 +4982,8 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이것</t>
+          <t xml:space="preserve">이
+것</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4984,7 +5011,8 @@
       </c>
       <c r="Q9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">어허</t>
+          <t xml:space="preserve">어
+허</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5036,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">느은</t>
+          <t xml:space="preserve">느
+은</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -5018,7 +5047,8 @@
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주어</t>
+          <t xml:space="preserve">주
+어</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -5029,7 +5059,8 @@
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈도</t>
+          <t xml:space="preserve">꿈
+도</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -5040,7 +5071,9 @@
       </c>
       <c r="K10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">저것이</t>
+          <t xml:space="preserve">저
+것
+이</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
@@ -5050,7 +5083,8 @@
       </c>
       <c r="M10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">두우</t>
+          <t xml:space="preserve">두
+우</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -5102,7 +5136,8 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -5113,7 +5148,8 @@
       </c>
       <c r="K11" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -5124,7 +5160,8 @@
       </c>
       <c r="M11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">가아</t>
+          <t xml:space="preserve">가
+아</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -5170,7 +5207,8 @@
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">가는</t>
+          <t xml:space="preserve">가
+는</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -5180,7 +5218,8 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">련만</t>
+          <t xml:space="preserve">련
+만</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -5191,7 +5230,8 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">로다</t>
+          <t xml:space="preserve">로
+다</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -5202,7 +5242,8 @@
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">꿈
+이</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -5218,7 +5259,8 @@
       </c>
       <c r="Q12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">어어</t>
+          <t xml:space="preserve">어
+어</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5299,8 @@
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">아안</t>
+          <t xml:space="preserve">아
+안</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -5275,7 +5318,8 @@
       </c>
       <c r="M13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">로다</t>
+          <t xml:space="preserve">로
+다</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -5318,7 +5362,8 @@
       </c>
       <c r="G14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">새영</t>
+          <t xml:space="preserve">새
+영</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -5328,7 +5373,8 @@
       </c>
       <c r="I14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">아ㄴ</t>
+          <t xml:space="preserve">아
+ㄴ</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,6 +253,33 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4441,7 +4473,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
@@ -4452,7 +4484,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -4463,7 +4495,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 에</t>
@@ -4475,7 +4507,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 깨</t>
@@ -4487,7 +4519,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 도</t>
@@ -4499,7 +4531,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -4511,7 +4543,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">성
 화</t>
@@ -4522,7 +4554,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4535,7 +4567,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 을</t>
@@ -4546,7 +4578,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -4557,7 +4589,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4568,7 +4600,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 나</t>
@@ -4580,7 +4612,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 도</t>
@@ -4592,7 +4624,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 다</t>
@@ -4603,13 +4635,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="35"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4622,13 +4654,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">았
 다</t>
@@ -4640,7 +4672,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 어</t>
@@ -4652,7 +4684,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4663,7 +4695,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 속</t>
@@ -4675,7 +4707,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -4686,7 +4718,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 아</t>
@@ -4697,7 +4729,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4710,7 +4742,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꾸</t>
         </is>
@@ -4720,14 +4752,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -4738,7 +4770,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이
@@ -4750,7 +4782,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4761,7 +4793,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 다</t>
@@ -4772,7 +4804,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
@@ -4783,7 +4815,7 @@
 △</t>
         </is>
       </c>
-      <c r="Q6" s="24"/>
+      <c r="Q6" s="34"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4792,7 +4824,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4802,13 +4834,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">살
 고</t>
@@ -4819,14 +4851,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">요
 오</t>
@@ -4837,13 +4869,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M7" s="25"/>
+      <c r="M7" s="35"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4853,7 +4885,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
@@ -4866,7 +4898,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">서
 어</t>
@@ -4877,7 +4909,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">써
 아</t>
@@ -4888,38 +4920,38 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="28"/>
+      <c r="I8" s="38"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="37"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="37"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O8" s="27"/>
+      <c r="O8" s="37"/>
       <c r="P8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q8" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 오</t>
@@ -4933,7 +4965,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4944,7 +4976,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">깨
 라</t>
@@ -4956,7 +4988,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 에</t>
@@ -4968,7 +5000,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">깨
 인</t>
@@ -4980,7 +5012,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 것</t>
@@ -4992,7 +5024,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
@@ -5003,13 +5035,13 @@
 姑</t>
         </is>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="33"/>
       <c r="P9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="24" t="inlineStr">
+      <c r="Q9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 허</t>
@@ -5023,7 +5055,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">엇</t>
         </is>
@@ -5034,7 +5066,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">느
 은</t>
@@ -5045,7 +5077,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">주
 어</t>
@@ -5057,7 +5089,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 도</t>
@@ -5069,7 +5101,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">저
 것
@@ -5081,7 +5113,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">두
 우</t>
@@ -5092,13 +5124,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="35"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="35"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -5107,7 +5139,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -5117,7 +5149,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
@@ -5128,13 +5160,13 @@
 △</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="27" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -5146,7 +5178,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -5158,7 +5190,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 아</t>
@@ -5169,13 +5201,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="37"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q11" s="27" t="inlineStr">
+      <c r="Q11" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5188,7 +5220,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5198,14 +5230,14 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E12" s="30"/>
+      <c r="E12" s="39"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 는</t>
@@ -5216,7 +5248,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">련
 만</t>
@@ -5228,7 +5260,7 @@
 汰</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 다</t>
@@ -5240,7 +5272,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈
 이</t>
@@ -5251,13 +5283,13 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q12" s="24" t="inlineStr">
+      <c r="Q12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 어</t>
@@ -5271,7 +5303,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5281,13 +5313,13 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
+      <c r="E13" s="40"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -5297,7 +5329,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 안</t>
@@ -5309,14 +5341,14 @@
 姑</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 다</t>
@@ -5327,14 +5359,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5348,19 +5380,19 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E14" s="32"/>
+      <c r="E14" s="41"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">새
 영</t>
@@ -5371,7 +5403,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 ㄴ</t>
@@ -5382,27 +5414,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="37"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="37"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="Q14" s="27" t="inlineStr">
+      <c r="Q14" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,52 +227,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -374,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">92</t>
         </is>
       </c>
     </row>
@@ -386,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
@@ -398,7 +354,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -422,7 +378,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔레트 외 글자 3, 비고 28%</t>
+          <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
     </row>
@@ -450,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굵은 선 3칸마다(3/4). 양식 용지번호 "- 197 -". 오른쪽 여백 제목 "흥 타령", 부제 "늦중모리". 하단 기호 설명: "姑 → 떠는음, 潢 → 꺾는음". 각 율명 줄 오른쪽 좁은 칸에 가사가 적혀 있어 그대로 전사함(후렴 "아이고 대고 어허~" 등). 2줄 머리에 "후렴" 표시와 아래쪽 화살표가 있음. 7줄(왼쪽에서 둘째 열) 10~12정간은 X로 크게 지워져 있어 비움(연주 안 함). 요성 물결선·덧칠이 많으며 기호표에 없는 꾸밈(세로 물결선 등)은 생략하고 비고에 남김. 손채보가 매우 빽빽하고 겹쳐 써 일부 칸 불확실. 줄 번호는 실제 열 위치(오른쪽부터 1~8).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'.</t>
         </is>
       </c>
     </row>
@@ -653,7 +609,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요성(떠는음)</t>
+          <t xml:space="preserve">姑 오른쪽 물결선(떠는음)</t>
         </is>
       </c>
       <c r="K2" s="2"/>
@@ -681,12 +637,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -720,12 +676,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -757,23 +713,19 @@
       <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|△</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">짧은 가로선 위, △ 아래</t>
-        </is>
-      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6">
@@ -799,12 +751,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -836,26 +788,22 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">고오</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -881,12 +829,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌^|潢</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌^
+潢</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -896,7 +845,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요성 물결선</t>
+          <t xml:space="preserve">㴌 오른쪽 작은 c 모양 꾸밈</t>
         </is>
       </c>
       <c r="K8" s="2"/>
@@ -924,12 +873,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -959,12 +908,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -996,26 +945,22 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어어</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -1041,13 +986,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1081,13 +1025,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|△</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-△</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1121,13 +1064,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1161,12 +1104,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1196,12 +1139,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1235,12 +1178,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1311,18 +1254,22 @@
       <c r="F19" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="4"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 오른쪽 세로 물결선</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1348,16 +1295,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1384,12 +1334,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1419,12 +1369,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1454,12 +1404,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1489,12 +1439,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1524,12 +1474,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1559,13 +1509,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1599,13 +1549,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1639,13 +1589,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1679,13 +1629,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1754,15 +1704,20 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1789,178 +1744,173 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모</t>
+        </is>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C33" s="2">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2">
+        <v>8</v>
+      </c>
+      <c r="F33" s="2">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">두우</t>
+        </is>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|潢</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가아</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C35" s="2">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+      <c r="F35" s="2">
+        <v>4</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|南</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈이</t>
+        </is>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C36" s="2">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2">
+        <v>11</v>
+      </c>
+      <c r="F36" s="2">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑|姑</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C33" s="2">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2">
-        <v>3</v>
-      </c>
-      <c r="E33" s="2">
-        <v>8</v>
-      </c>
-      <c r="F33" s="2">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두우</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|潢</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가아</t>
-        </is>
-      </c>
-      <c r="J34" s="4"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C35" s="2">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2">
-        <v>3</v>
-      </c>
-      <c r="E35" s="2">
-        <v>10</v>
-      </c>
-      <c r="F35" s="2">
-        <v>4</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈이</t>
-        </is>
-      </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <v>1</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C36" s="2">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2">
-        <v>11</v>
-      </c>
-      <c r="F36" s="2">
-        <v>4</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">로다</t>
@@ -1990,19 +1940,23 @@
       <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|△</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 가 6 모양으로 그려짐(○?)</t>
+        </is>
+      </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -2039,7 +1993,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나도</t>
+          <t xml:space="preserve">너도</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2108,12 +2062,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|潢</t>
+          <t xml:space="preserve">南|潢</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
@@ -2148,17 +2102,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J41" s="4"/>
@@ -2187,13 +2141,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|汰</t>
+          <t xml:space="preserve">汰|㴌</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰</t>
+㴌</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2225,19 +2179,23 @@
       <c r="F43" s="2">
         <v>2</v>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–|△</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="4"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 옆 세로 물결선</t>
+        </is>
+      </c>
       <c r="K43" s="2"/>
     </row>
     <row r="44">
@@ -2263,13 +2221,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|汰</t>
+          <t xml:space="preserve">汰|㴌</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰</t>
+㴌</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2303,23 +2261,23 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">△|㴌</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">△
+㴌</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">저것이</t>
+          <t xml:space="preserve">저</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요성 물결선</t>
+          <t xml:space="preserve">㴌 위 작은 △, 둥근 선 겹침</t>
         </is>
       </c>
       <c r="K45" s="2"/>
@@ -2358,12 +2316,12 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">것이</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요성 물결선</t>
+          <t xml:space="preserve">덧칠 겹침</t>
         </is>
       </c>
       <c r="K46" s="2"/>
@@ -2389,23 +2347,27 @@
       <c r="F47" s="2">
         <v>4</v>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|汰</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|潢</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로다</t>
-        </is>
-      </c>
-      <c r="J47" s="4"/>
+潢</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈이</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">윗 潢 왼쪽 &lt; 모양</t>
+        </is>
+      </c>
       <c r="K47" s="2"/>
     </row>
     <row r="48">
@@ -2431,16 +2393,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로다</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2467,12 +2433,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2542,12 +2509,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
+          <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
@@ -2580,27 +2547,23 @@
       <c r="F52" s="2">
         <v>1</v>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">또꿈</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
     <row r="53">
@@ -2626,17 +2589,18 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+潢</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이오</t>
+          <t xml:space="preserve">이요</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2663,18 +2627,22 @@
       <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 옆 긴 곡선</t>
+        </is>
+      </c>
       <c r="K54" s="2"/>
     </row>
     <row r="55">
@@ -2698,22 +2666,22 @@
       <c r="F55" s="2">
         <v>2</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I55" s="3"/>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오오</t>
+        </is>
+      </c>
+      <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2737,27 +2705,23 @@
       <c r="F56" s="2">
         <v>3</v>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|汰</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|潢</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">깨인</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
     <row r="57">
@@ -2783,13 +2747,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -2823,12 +2787,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|潢</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南
+潢</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2862,12 +2827,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2899,26 +2865,22 @@
       <c r="F60" s="2">
         <v>4</v>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아안</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
     <row r="61">
@@ -2942,26 +2904,22 @@
       <c r="F61" s="2">
         <v>4</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아ㄴ</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+      <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
     <row r="62">
@@ -2987,138 +2945,138 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">南|南</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈에</t>
+        </is>
+      </c>
+      <c r="J62" s="4"/>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>1</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C63" s="2">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2">
+        <v>6</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|潢</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나서어</t>
+        </is>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>1</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C64" s="2">
+        <v>6</v>
+      </c>
+      <c r="D64" s="2">
+        <v>6</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|姑</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+姑</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈에</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>1</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="C65" s="2">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2">
+        <v>6</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4</v>
+      </c>
+      <c r="F65" s="2">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑|姑</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈에</t>
-        </is>
-      </c>
-      <c r="J62" s="4"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>1</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C63" s="2">
-        <v>6</v>
-      </c>
-      <c r="D63" s="2">
-        <v>6</v>
-      </c>
-      <c r="E63" s="2">
-        <v>2</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|潢</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="J63" s="4"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2">
-        <v>1</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C64" s="2">
-        <v>6</v>
-      </c>
-      <c r="D64" s="2">
-        <v>6</v>
-      </c>
-      <c r="E64" s="2">
-        <v>3</v>
-      </c>
-      <c r="F64" s="2">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서어</t>
-        </is>
-      </c>
-      <c r="J64" s="4"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>1</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C65" s="2">
-        <v>6</v>
-      </c>
-      <c r="D65" s="2">
-        <v>6</v>
-      </c>
-      <c r="E65" s="2">
-        <v>4</v>
-      </c>
-      <c r="F65" s="2">
-        <v>2</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈이</t>
+          <t xml:space="preserve">살고</t>
         </is>
       </c>
       <c r="J65" s="4"/>
@@ -3147,22 +3105,18 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">살고</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I66" s="3"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">세로 요성 물결선 겹침</t>
+          <t xml:space="preserve">세로 물결선</t>
         </is>
       </c>
       <c r="K66" s="2"/>
@@ -3188,18 +3142,22 @@
       <c r="F67" s="2">
         <v>2</v>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세로 물결선</t>
+        </is>
+      </c>
       <c r="K67" s="2"/>
     </row>
     <row r="68">
@@ -3225,13 +3183,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3263,26 +3221,23 @@
       <c r="F69" s="2">
         <v>3</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주어</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">죽어</t>
+        </is>
+      </c>
+      <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
     <row r="70">
@@ -3306,19 +3261,23 @@
       <c r="F70" s="2">
         <v>3</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|△</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I70" s="2"/>
-      <c r="J70" s="4"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세로 물결선</t>
+        </is>
+      </c>
       <c r="K70" s="2"/>
     </row>
     <row r="71">
@@ -3344,13 +3303,13 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|汰</t>
+          <t xml:space="preserve">湳|湳</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-汰</t>
+          <t xml:space="preserve">湳
+湳</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3384,12 +3343,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3421,26 +3380,22 @@
       <c r="F73" s="2">
         <v>4</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새영</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 흘림, 새영/생? 불확실</t>
-        </is>
-      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새앵</t>
+        </is>
+      </c>
+      <c r="J73" s="4"/>
       <c r="K73" s="2"/>
     </row>
     <row r="74">
@@ -3464,27 +3419,23 @@
       <c r="F74" s="2">
         <v>1</v>
       </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|㴌</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부질</t>
+        </is>
+      </c>
+      <c r="J74" s="4"/>
       <c r="K74" s="2"/>
     </row>
     <row r="75">
@@ -3508,26 +3459,23 @@
       <c r="F75" s="2">
         <v>1</v>
       </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|㴌</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없다</t>
+        </is>
+      </c>
+      <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
     <row r="76">
@@ -3553,22 +3501,18 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">았다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I76" s="3"/>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">세로 요성 물결선, 가사 않다/았다?</t>
+          <t xml:space="preserve">세로 물결선</t>
         </is>
       </c>
       <c r="K76" s="2"/>
@@ -3596,18 +3540,18 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">세로 요성 물결선</t>
+          <t xml:space="preserve">세로 물결선</t>
         </is>
       </c>
       <c r="K77" s="2"/>
@@ -3628,22 +3572,26 @@
         <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F78" s="2">
         <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3663,29 +3611,30 @@
         <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳|湳</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳
+湳</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">써아</t>
+          <t xml:space="preserve">깨라</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요성 물결선</t>
+          <t xml:space="preserve">가사 라/랴?</t>
         </is>
       </c>
       <c r="K79" s="2"/>
@@ -3706,25 +3655,25 @@
         <v>7</v>
       </c>
       <c r="E80" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2">
         <v>3</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">㴌|潢</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">㴌
+潢</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨라</t>
+          <t xml:space="preserve">느은</t>
         </is>
       </c>
       <c r="J80" s="4"/>
@@ -3746,25 +3695,24 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" s="2">
         <v>3</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">느은</t>
+          <t xml:space="preserve">꿈</t>
         </is>
       </c>
       <c r="J81" s="4"/>
@@ -3780,30 +3728,31 @@
         </is>
       </c>
       <c r="C82" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E82" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南
+南</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈</t>
+          <t xml:space="preserve">꿈을</t>
         </is>
       </c>
       <c r="J82" s="4"/>
@@ -3819,38 +3768,30 @@
         </is>
       </c>
       <c r="C83" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E83" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F83" s="2">
-        <v>4</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I83" s="5"/>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">칸이 X로 크게 지워짐(연주 안 함)</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
@@ -3862,38 +3803,34 @@
         </is>
       </c>
       <c r="C84" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E84" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F84" s="2">
-        <v>4</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I84" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">칸이 X로 크게 지워짐(연주 안 함)</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+          <t xml:space="preserve">비스듬한 짧은 선</t>
+        </is>
+      </c>
+      <c r="K84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
@@ -3905,38 +3842,34 @@
         </is>
       </c>
       <c r="C85" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F85" s="2">
-        <v>4</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I85" s="5"/>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">칸이 X로 크게 지워짐(연주 안 함)</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꾸</t>
+        </is>
+      </c>
+      <c r="J85" s="4"/>
+      <c r="K85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
@@ -3954,25 +3887,24 @@
         <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">꿈</t>
+          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J86" s="4"/>
@@ -3994,24 +3926,24 @@
         <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F87" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">으을</t>
+          <t xml:space="preserve">서어</t>
         </is>
       </c>
       <c r="J87" s="4"/>
@@ -4033,22 +3965,26 @@
         <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I88" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
       <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
@@ -4068,24 +4004,24 @@
         <v>8</v>
       </c>
       <c r="E89" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">꾸</t>
+          <t xml:space="preserve">엇</t>
         </is>
       </c>
       <c r="J89" s="4"/>
@@ -4107,24 +4043,24 @@
         <v>8</v>
       </c>
       <c r="E90" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F90" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">을</t>
         </is>
       </c>
       <c r="J90" s="4"/>
@@ -4146,31 +4082,27 @@
         <v>8</v>
       </c>
       <c r="E91" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F91" s="2">
-        <v>2</v>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서어</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
     <row r="92">
@@ -4189,10 +4121,10 @@
         <v>8</v>
       </c>
       <c r="E92" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F92" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -4206,7 +4138,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무</t>
+          <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="J92" s="4"/>
@@ -4228,192 +4160,28 @@
         <v>8</v>
       </c>
       <c r="E93" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F93" s="2">
-        <v>3</v>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엇</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I93" s="2"/>
+      <c r="J93" s="4"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>1</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C94" s="2">
-        <v>8</v>
-      </c>
-      <c r="D94" s="2">
-        <v>8</v>
-      </c>
-      <c r="E94" s="2">
-        <v>9</v>
-      </c>
-      <c r="F94" s="2">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성 물결선</t>
-        </is>
-      </c>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>1</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C95" s="2">
-        <v>8</v>
-      </c>
-      <c r="D95" s="2">
-        <v>8</v>
-      </c>
-      <c r="E95" s="2">
-        <v>10</v>
-      </c>
-      <c r="F95" s="2">
-        <v>4</v>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J95" s="4"/>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>1</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C96" s="2">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2">
-        <v>8</v>
-      </c>
-      <c r="E96" s="2">
-        <v>11</v>
-      </c>
-      <c r="F96" s="2">
-        <v>4</v>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="J96" s="4"/>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2">
-        <v>1</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
-      </c>
-      <c r="C97" s="2">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2">
-        <v>8</v>
-      </c>
-      <c r="E97" s="2">
-        <v>12</v>
-      </c>
-      <c r="F97" s="2">
-        <v>4</v>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|△</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
-△</t>
-        </is>
-      </c>
-      <c r="I97" s="2"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K97"/>
+  <autoFilter ref="A1:K93"/>
 </worksheet>
 </file>
 
@@ -4442,7 +4210,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="55.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4465,976 +4233,968 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="55.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+을</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부
+질</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+에</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+깨</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+汰</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">너
+도</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+이</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성
+화</t>
+        </is>
+      </c>
+      <c r="P3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55.96" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없
+다</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+서
+어</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+나</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+汰</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+도</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로
+다</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55.96" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+姑</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+에</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">또
+꿈</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+속</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+이</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+아</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55.96" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꾸</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">살
+고</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+요</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로
+다</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">났</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q6" s="22"/>
+    </row>
+    <row r="7" ht="55.96" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G7" s="28"/>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I7" s="28"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+㴌</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요
+오</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55.96" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서
+어</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오
+오</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고
+오</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55.96" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+湳</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깨
+라</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+에</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깨
+인</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+것</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌^
+潢</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어
+허</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55.96" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느
+은</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">죽
+어</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+도</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△
+㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">두
+우</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q10" s="25"/>
+    </row>
+    <row r="11" ht="55.96" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+이</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">것
+이</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+潢</t>
+        </is>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+아</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55.96" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+湳</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+는</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">련
+만</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+이</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈
+이</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55.96" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리</t>
+        </is>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+안</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로
+다</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-에</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-깨</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-汰</t>
-        </is>
-      </c>
-      <c r="K3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나
-도</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="O3" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성
-화</t>
-        </is>
-      </c>
-      <c r="P3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">으
-을</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E4" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="G4" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-潢</t>
-        </is>
-      </c>
-      <c r="I4" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-나</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-汰</t>
-        </is>
-      </c>
-      <c r="K4" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나
-도</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M4" s="35" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">로
 다</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="35"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E5" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">았
-다</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="G5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서
-어</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I5" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="K5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-속</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가
-아</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꾸</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이
-오</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로
-다</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">났</t>
-        </is>
-      </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55.96" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q6" s="34"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G7" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">살
-고</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-汰</t>
-        </is>
-      </c>
-      <c r="K7" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요
-오</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q7" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서
-어</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">써
-아</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새
+앵</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="K8" s="37"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M8" s="37"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O8" s="37"/>
-      <c r="P8" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q8" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고
-오</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깨
-라</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="G9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-에</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I9" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깨
-인</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-汰</t>
-        </is>
-      </c>
-      <c r="K9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-것</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M9" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">모</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="O9" s="33"/>
-      <c r="P9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q9" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어
-허</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엇</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">느
-은</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주
-어</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="I10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-도</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="K10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">저
-것
-이</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M10" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두
-우</t>
-        </is>
-      </c>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="35"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q10" s="35"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="K11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="M11" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가
-아</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O11" s="37"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q11" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-汰</t>
-        </is>
-      </c>
-      <c r="G12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가
-는</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">련
-만</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="K12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로
-다</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M12" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈
-이</t>
-        </is>
-      </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="33"/>
-      <c r="P12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어
-어</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G13" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인</t>
-        </is>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-안</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="K13" s="35"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="M13" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로
-다</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="35"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="Q13" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G14" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">새
-영</t>
-        </is>
-      </c>
-      <c r="H14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I14" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-ㄴ</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="37"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="M14" s="37"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O14" s="37"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-△</t>
-        </is>
-      </c>
-      <c r="Q14" s="37" t="inlineStr">
+      <c r="Q14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>

--- a/sheets/민요/검수/흥 타령 (늦중모리).xlsx
+++ b/sheets/민요/검수/흥 타령 (늦중모리).xlsx
@@ -406,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
